--- a/config/Configuration.xlsx
+++ b/config/Configuration.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Mission" sheetId="1" state="visible" r:id="rId3"/>
@@ -13,11 +13,11 @@
     <sheet name="Target" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="Agent" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="Tracking" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Head" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="Window" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="MultiCamera" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="MultiWindow" sheetId="7" state="visible" r:id="rId9"/>
     <sheet name="Drone" sheetId="8" state="visible" r:id="rId10"/>
-    <sheet name="Gimbal" sheetId="9" state="visible" r:id="rId11"/>
-    <sheet name="Camera" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="Camera" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="Gimbal" sheetId="10" state="visible" r:id="rId12"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="274">
   <si>
     <t xml:space="preserve">GENERAL CONFIGURATION</t>
   </si>
@@ -64,96 +64,96 @@
     <t xml:space="preserve">StartHour</t>
   </si>
   <si>
+    <t xml:space="preserve">MISSION00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mission S01 (Multi-Camera)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENVIRONMENT00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GROUP00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEAM00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(-150.0, 150.0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(30.0, 150.0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PX4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(13/12/2024)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(16:30:00)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MISSION01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mission S02 (Multi-Camera)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GROUP01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEAM01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MISSION02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mission S03 (Multi-Camera)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENVIRONMENT01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GROUP02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEAM02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MISSION03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mission S04 (Multi-Camera)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GROUP03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEAM03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MISSION04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mission S01 (Multi-Window)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEAM04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MISSION05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mission S02 (Multi-Window)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEAM05</t>
+  </si>
+  <si>
     <t xml:space="preserve">X</t>
   </si>
   <si>
-    <t xml:space="preserve">MISSION00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mission S01 (Multi-Camera)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENVIRONMENT00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GROUP00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TEAM00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(-150.0, 150.0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(30.0, 150.0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PX4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(13/12/2024)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(16:30:00)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MISSION01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mission S02 (Multi-Camera)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GROUP01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TEAM01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MISSION02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mission S03 (Multi-Camera)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENVIRONMENT01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GROUP02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TEAM02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MISSION03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mission S04 (Multi-Camera)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GROUP03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TEAM03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MISSION04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mission S01 (Multi-Window)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TEAM04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MISSION05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mission S02 (Multi-Window)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TEAM05</t>
-  </si>
-  <si>
     <t xml:space="preserve">MISSION06</t>
   </si>
   <si>
@@ -253,12 +253,6 @@
     <t xml:space="preserve">TrackingID</t>
   </si>
   <si>
-    <t xml:space="preserve">HeadSetID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WindowSetID</t>
-  </si>
-  <si>
     <t xml:space="preserve">DroneID</t>
   </si>
   <si>
@@ -286,12 +280,6 @@
     <t xml:space="preserve">TRACKING00</t>
   </si>
   <si>
-    <t xml:space="preserve">HEADSET00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-</t>
-  </si>
-  <si>
     <t xml:space="preserve">DRONE00</t>
   </si>
   <si>
@@ -310,9 +298,6 @@
     <t xml:space="preserve">TRACKING01</t>
   </si>
   <si>
-    <t xml:space="preserve">HEADSET01</t>
-  </si>
-  <si>
     <t xml:space="preserve">AGENT02</t>
   </si>
   <si>
@@ -322,9 +307,6 @@
     <t xml:space="preserve">TRACKING02</t>
   </si>
   <si>
-    <t xml:space="preserve">HEADSET02</t>
-  </si>
-  <si>
     <t xml:space="preserve">DRONE01</t>
   </si>
   <si>
@@ -337,9 +319,6 @@
     <t xml:space="preserve">TRACKING03</t>
   </si>
   <si>
-    <t xml:space="preserve">HEADSET03</t>
-  </si>
-  <si>
     <t xml:space="preserve">AGENT04</t>
   </si>
   <si>
@@ -349,12 +328,6 @@
     <t xml:space="preserve">TRACKING04</t>
   </si>
   <si>
-    <t xml:space="preserve">HEADSET04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WINDOWSET00</t>
-  </si>
-  <si>
     <t xml:space="preserve">AGENT05</t>
   </si>
   <si>
@@ -364,12 +337,6 @@
     <t xml:space="preserve">TRACKING05</t>
   </si>
   <si>
-    <t xml:space="preserve">HEADSET05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WINDOWSET01</t>
-  </si>
-  <si>
     <t xml:space="preserve">AGENT06</t>
   </si>
   <si>
@@ -379,12 +346,6 @@
     <t xml:space="preserve">TRACKING06</t>
   </si>
   <si>
-    <t xml:space="preserve">HEADSET06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WINDOWSET02</t>
-  </si>
-  <si>
     <t xml:space="preserve">AGENT07</t>
   </si>
   <si>
@@ -394,13 +355,7 @@
     <t xml:space="preserve">TRACKING07</t>
   </si>
   <si>
-    <t xml:space="preserve">HEADSET07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WINDOWSET03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mode</t>
+    <t xml:space="preserve">ObservationSetID</t>
   </si>
   <si>
     <t xml:space="preserve">MinTargetSize</t>
@@ -415,39 +370,57 @@
     <t xml:space="preserve">Tracking S01 (Multi-Camera)</t>
   </si>
   <si>
-    <t xml:space="preserve">MultiCamera</t>
+    <t xml:space="preserve">SET00</t>
   </si>
   <si>
     <t xml:space="preserve">Tracking S02 (Multi-Camera)</t>
   </si>
   <si>
+    <t xml:space="preserve">SET01</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tracking S03 (Multi-Camera)</t>
   </si>
   <si>
+    <t xml:space="preserve">SET02</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tracking S04 (Multi-Camera)</t>
   </si>
   <si>
+    <t xml:space="preserve">SET03</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tracking S01 (Multi-Window)</t>
   </si>
   <si>
-    <t xml:space="preserve">MultiWindow</t>
+    <t xml:space="preserve">SET04</t>
   </si>
   <si>
     <t xml:space="preserve">Tracking S02 (Multi-Window)</t>
   </si>
   <si>
+    <t xml:space="preserve">SET05</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tracking S03 (Multi-Window)</t>
   </si>
   <si>
+    <t xml:space="preserve">SET06</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tracking S04 (Multi-Window)</t>
   </si>
   <si>
+    <t xml:space="preserve">SET07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CameraID</t>
+  </si>
+  <si>
     <t xml:space="preserve">GimbalID</t>
   </si>
   <si>
-    <t xml:space="preserve">CameraID</t>
-  </si>
-  <si>
     <t xml:space="preserve">Role</t>
   </si>
   <si>
@@ -460,18 +433,18 @@
     <t xml:space="preserve">RefFocal [mm]</t>
   </si>
   <si>
-    <t xml:space="preserve">HEAD00</t>
+    <t xml:space="preserve">MULTICAMERA00</t>
   </si>
   <si>
     <t xml:space="preserve">Central Head S01 (Multi-Camera)</t>
   </si>
   <si>
+    <t xml:space="preserve">CAM00</t>
+  </si>
+  <si>
     <t xml:space="preserve">GIM00</t>
   </si>
   <si>
-    <t xml:space="preserve">CAM00</t>
-  </si>
-  <si>
     <t xml:space="preserve">Central</t>
   </si>
   <si>
@@ -481,7 +454,7 @@
     <t xml:space="preserve">(Roll=0.0, Pitch=90.0, Yaw=90.0)</t>
   </si>
   <si>
-    <t xml:space="preserve">HEAD01</t>
+    <t xml:space="preserve">MULTICAMERA01</t>
   </si>
   <si>
     <t xml:space="preserve">Tracking Head 1 S01 (Multi-Camera)</t>
@@ -499,7 +472,7 @@
     <t xml:space="preserve">(Roll=0.0, Pitch=90.0, Yaw=0.0)</t>
   </si>
   <si>
-    <t xml:space="preserve">HEAD02</t>
+    <t xml:space="preserve">MULTICAMERA02</t>
   </si>
   <si>
     <t xml:space="preserve">Tracking Head 2 S01 (Multi-Camera)</t>
@@ -508,25 +481,25 @@
     <t xml:space="preserve">(X=0.0, Y=0.3, Z=-0.15)</t>
   </si>
   <si>
-    <t xml:space="preserve">HEAD03</t>
+    <t xml:space="preserve">MULTICAMERA03</t>
   </si>
   <si>
     <t xml:space="preserve">Central Head S02 (Multi-Camera)</t>
   </si>
   <si>
-    <t xml:space="preserve">HEAD04</t>
+    <t xml:space="preserve">MULTICAMERA04</t>
   </si>
   <si>
     <t xml:space="preserve">Tracking Head 1 S02 (Multi-Camera)</t>
   </si>
   <si>
-    <t xml:space="preserve">HEAD05</t>
+    <t xml:space="preserve">MULTICAMERA05</t>
   </si>
   <si>
     <t xml:space="preserve">Tracking Head 2 S02 (Multi-Camera)</t>
   </si>
   <si>
-    <t xml:space="preserve">HEAD06</t>
+    <t xml:space="preserve">MULTICAMERA06</t>
   </si>
   <si>
     <t xml:space="preserve">Central Head S03 (Multi-Camera)</t>
@@ -535,7 +508,7 @@
     <t xml:space="preserve">CAM02</t>
   </si>
   <si>
-    <t xml:space="preserve">HEAD07</t>
+    <t xml:space="preserve">MULTICAMERA07</t>
   </si>
   <si>
     <t xml:space="preserve">Tracking Head 1 S03 (Multi-Camera)</t>
@@ -544,13 +517,13 @@
     <t xml:space="preserve">CAM03</t>
   </si>
   <si>
-    <t xml:space="preserve">HEAD08</t>
+    <t xml:space="preserve">MULTICAMERA08</t>
   </si>
   <si>
     <t xml:space="preserve">Tracking Head 2 S03 (Multi-Camera)</t>
   </si>
   <si>
-    <t xml:space="preserve">HEAD09</t>
+    <t xml:space="preserve">MULTICAMERA09</t>
   </si>
   <si>
     <t xml:space="preserve">Tracking Head 3 S03 (Multi-Camera)</t>
@@ -562,31 +535,31 @@
     <t xml:space="preserve">(Roll=0.0, Pitch=90.0, Yaw=180.0)</t>
   </si>
   <si>
-    <t xml:space="preserve">HEAD10</t>
+    <t xml:space="preserve">MULTICAMERA10</t>
   </si>
   <si>
     <t xml:space="preserve">Central Head S04 (Multi-Camera)</t>
   </si>
   <si>
-    <t xml:space="preserve">HEAD11</t>
+    <t xml:space="preserve">MULTICAMERA11</t>
   </si>
   <si>
     <t xml:space="preserve">Tracking Head 1 S04 (Multi-Camera)</t>
   </si>
   <si>
-    <t xml:space="preserve">HEAD12</t>
+    <t xml:space="preserve">MULTICAMERA12</t>
   </si>
   <si>
     <t xml:space="preserve">Tracking Head 2 S04 (Multi-Camera)</t>
   </si>
   <si>
-    <t xml:space="preserve">HEAD13</t>
+    <t xml:space="preserve">MULTICAMERA13</t>
   </si>
   <si>
     <t xml:space="preserve">Tracking Head 3 S04 (Multi-Camera)</t>
   </si>
   <si>
-    <t xml:space="preserve">HEAD14</t>
+    <t xml:space="preserve">MULTICAMERA14</t>
   </si>
   <si>
     <t xml:space="preserve">Tracking Head 4 S04 (Multi-Camera)</t>
@@ -598,7 +571,7 @@
     <t xml:space="preserve">(Roll=0.0, Pitch=90.0, Yaw=270.0)</t>
   </si>
   <si>
-    <t xml:space="preserve">HEAD15</t>
+    <t xml:space="preserve">MULTICAMERA15</t>
   </si>
   <si>
     <t xml:space="preserve">Central Head S01 (Multi-Window)</t>
@@ -607,13 +580,13 @@
     <t xml:space="preserve">CAM04</t>
   </si>
   <si>
-    <t xml:space="preserve">HEAD16</t>
+    <t xml:space="preserve">MULTICAMERA16</t>
   </si>
   <si>
     <t xml:space="preserve">Central Head S02 (Multi-Window)</t>
   </si>
   <si>
-    <t xml:space="preserve">HEAD17</t>
+    <t xml:space="preserve">MULTICAMERA17</t>
   </si>
   <si>
     <t xml:space="preserve">Central Head S03 (Multi-Window)</t>
@@ -622,7 +595,7 @@
     <t xml:space="preserve">CAM05</t>
   </si>
   <si>
-    <t xml:space="preserve">HEAD18</t>
+    <t xml:space="preserve">MULTICAMERA18</t>
   </si>
   <si>
     <t xml:space="preserve">Central Head S04 (Multi-Window)</t>
@@ -640,175 +613,214 @@
     <t xml:space="preserve">RefLambda</t>
   </si>
   <si>
-    <t xml:space="preserve">WINDOW00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Central Window S01 (Multi-Window)</t>
+    <t xml:space="preserve">MULTIWINDOW00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tracking Window 1 S01 (Multi-Window)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(480x270)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTIWINDOW01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tracking Window 2 S01 (Multi-Window)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTIWINDOW02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tracking Window 1 S02 (Multi-Window)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTIWINDOW03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tracking Window 2 S02 (Multi-Window)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTIWINDOW04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tracking Window 1 S03 (Multi-Window)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTIWINDOW05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tracking Window 2 S03 (Multi-Window)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTIWINDOW06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tracking Window 3 S03 (Multi-Window)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTIWINDOW07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tracking Window 1 S04 (Multi-Window)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTIWINDOW08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tracking Window 2 S04 (Multi-Window)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTIWINDOW09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tracking Window 3 S04 (Multi-Window)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTIWINDOW10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tracking Window 4 S04 (Multi-Window)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HARDWARE CATALOGS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CruiseSpeed [m/s]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxSpeed [m/s]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EnableBarometer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barometer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EnableIMU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EnableGPS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GPS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EnableMagnetometer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magnetometer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BaseWeight [kg]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxPayloadWeight [kg]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HoverPower [W]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CruisePower [W]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LoadFactor [W/kg]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hexacopter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(WhiteNoiseSigma=2.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(AngularWhiteNoiseSigma=0.3, VelocityWhiteNoiseSigma=0.24)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(EphIni=25, EpvIni=25, EphFin=0.1, EpvFin=0.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(WhiteNoiseSigma=0.005, WhiteNoiseBias=0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(WhiteNoiseSigma=8.0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(AngularWhiteNoiseSigma=0.8, VelocityWhiteNoiseSigma=0.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(EphIni=50, EpvIni=50, EphFin=2.0, EpvFin=2.0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(WhiteNoiseSigma=0.02, WhiteNoiseBias=0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SensorSize [mm]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distortion (K1, K2, K3, P1, P2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EnableSensorNoise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SensorNoise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weight [kg]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IdlePower [W]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ActivePower [W]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operational Conditions O1 (low-resolution central camera)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RGB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1920x1080)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(13.2x7.425)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(-0.03, 0.002, 0.0, 0.0005, -0.0004)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(RandContrib=0.001, RandSize=100, RandSpeed=50000)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operational Conditions O1 (low-resolution tracking camera)</t>
   </si>
   <si>
     <t xml:space="preserve">(1280x720)</t>
   </si>
   <si>
-    <t xml:space="preserve">WINDOW01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tracking Window 1 S01 (Multi-Window)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(480x270)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WINDOW02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tracking Window 2 S01 (Multi-Window)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WINDOW03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Central Window S02 (Multi-Window)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WINDOW04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tracking Window 1 S02 (Multi-Window)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WINDOW05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tracking Window 2 S02 (Multi-Window)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WINDOW06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Central Window S03 (Multi-Window)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WINDOW07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tracking Window 1 S03 (Multi-Window)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WINDOW08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tracking Window 2 S03 (Multi-Window)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WINDOW09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tracking Window 3 S03 (Multi-Window)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WINDOW10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Central Window S04 (Multi-Window)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WINDOW11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tracking Window 1 S04 (Multi-Window)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WINDOW12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tracking Window 2 S04 (Multi-Window)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WINDOW13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tracking Window 3 S04 (Multi-Window)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WINDOW14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tracking Window 4 S04 (Multi-Window)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HARDWARE CATALOGS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CruiseSpeed [m/s]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MaxSpeed [m/s]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EnableBarometer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barometer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EnableIMU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IMU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EnableGPS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GPS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EnableMagnetometer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magnetometer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BaseWeight [kg]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MaxPayloadWeight [kg]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HoverPower [W]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CruisePower [W]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LoadFactor [W/kg]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hexacopter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(WhiteNoiseSigma=2.7)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(AngularWhiteNoiseSigma=0.3, VelocityWhiteNoiseSigma=0.24)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(EphIni=25, EpvIni=25, EphFin=0.1, EpvFin=0.1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(WhiteNoiseSigma=0.005, WhiteNoiseBias=0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(WhiteNoiseSigma=8.0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(AngularWhiteNoiseSigma=0.8, VelocityWhiteNoiseSigma=0.6)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(EphIni=50, EpvIni=50, EphFin=2.0, EpvFin=2.0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(WhiteNoiseSigma=0.02, WhiteNoiseBias=0)</t>
+    <t xml:space="preserve">Operational Conditions O2 (low-resolution central camera)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(-0.08, 0.008, 0.0001, 0.002, -0.0015)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(RandContrib=0.003, RandSize=200, RandSpeed=70000)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operational Conditions O2 (low-resolution tracking camera)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operational Conditions O1 (ultra-high-resolution camera)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(7680x4320)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operational Conditions O2 (ultra-high-resolution camera)</t>
   </si>
   <si>
     <t xml:space="preserve">EnableRoll</t>
@@ -829,15 +841,6 @@
     <t xml:space="preserve">Yaw</t>
   </si>
   <si>
-    <t xml:space="preserve">Weight [kg]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IdlePower [W]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ActivePower [W]</t>
-  </si>
-  <si>
     <t xml:space="preserve">Default Gimbal</t>
   </si>
   <si>
@@ -848,60 +851,6 @@
   </si>
   <si>
     <t xml:space="preserve">(Min=-320.0, Max=320.0, Speed=270)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SensorSize [mm]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Distortion (K1, K2, K3, P1, P2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EnableSensorNoise</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SensorNoise</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operational Conditions O1 (low-resolution central camera)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RGB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(1920x1080)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(13.2x7.425)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(-0.03, 0.002, 0.0, 0.0005, -0.0004)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(RandContrib=0.001, RandSize=100, RandSpeed=50000)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operational Conditions O1 (low-resolution tracking camera)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operational Conditions O2 (low-resolution central camera)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(-0.08, 0.008, 0.0001, 0.002, -0.0015)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(RandContrib=0.003, RandSize=200, RandSpeed=70000)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operational Conditions O2 (low-resolution tracking camera)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operational Conditions O1 (ultra-high-resolution camera)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(7680x4320)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operational Conditions O2 (ultra-high-resolution camera)</t>
   </si>
 </sst>
 </file>
@@ -976,21 +925,20 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
-      <sz val="16"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color theme="2" tint="-0.75"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1012,13 +960,19 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.7999"/>
-        <bgColor rgb="FFCCFFFF"/>
+        <bgColor rgb="FFDDE8CB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.3999"/>
-        <bgColor rgb="FF99CCFF"/>
+        <fgColor rgb="FFAFD095"/>
+        <bgColor rgb="FFDDE8CB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDE8CB"/>
+        <bgColor rgb="FFDAE3F3"/>
       </patternFill>
     </fill>
     <fill>
@@ -1075,7 +1029,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1108,7 +1062,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1120,7 +1074,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1144,23 +1098,27 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1201,7 +1159,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFA9D18E"/>
+          <fgColor rgb="FFAFD095"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -1209,6 +1167,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFDDE8CB"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -1246,7 +1205,7 @@
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFA9D18E"/>
+      <rgbColor rgb="FFAFD095"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF8FAADC"/>
       <rgbColor rgb="FF993366"/>
@@ -1266,7 +1225,7 @@
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFDDE8CB"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
@@ -1294,21 +1253,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table2" displayName="Table2" ref="A2:L2" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A2:L2"/>
-  <tableColumns count="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table2" displayName="Table2" ref="A2:J2" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A2:J2"/>
+  <tableColumns count="10">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Name"/>
     <tableColumn id="3" name="AgentTeamID"/>
     <tableColumn id="4" name="TrackingID"/>
-    <tableColumn id="5" name="HeadSetID"/>
-    <tableColumn id="6" name="WindowSetID"/>
-    <tableColumn id="7" name="DroneID"/>
-    <tableColumn id="8" name="Position [m]"/>
-    <tableColumn id="9" name="Orientation [°]"/>
-    <tableColumn id="10" name="MaxAltitude [m]"/>
-    <tableColumn id="11" name="SafetyRadius [m]"/>
-    <tableColumn id="12" name="BatteryCapacity [mAh]"/>
+    <tableColumn id="5" name="DroneID"/>
+    <tableColumn id="6" name="Position [m]"/>
+    <tableColumn id="7" name="Orientation [°]"/>
+    <tableColumn id="8" name="MaxAltitude [m]"/>
+    <tableColumn id="9" name="SafetyRadius [m]"/>
+    <tableColumn id="10" name="BatteryCapacity [mAh]"/>
   </tableColumns>
 </table>
 </file>
@@ -1335,9 +1292,9 @@
   <tableColumns count="10">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Name"/>
-    <tableColumn id="3" name="HeadSetID"/>
-    <tableColumn id="4" name="GimbalID"/>
-    <tableColumn id="5" name="CameraID"/>
+    <tableColumn id="3" name="ObservationSetID"/>
+    <tableColumn id="4" name="CameraID"/>
+    <tableColumn id="5" name="GimbalID"/>
     <tableColumn id="6" name="Role"/>
     <tableColumn id="7" name="Position [m]"/>
     <tableColumn id="8" name="Orientation [°]"/>
@@ -1348,17 +1305,16 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table210_2" displayName="Table210_2" ref="A2:H16" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A2:H16"/>
-  <tableColumns count="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table210_2" displayName="Table210_2" ref="A2:G12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A2:G12"/>
+  <tableColumns count="7">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Name"/>
-    <tableColumn id="3" name="WindowSetID"/>
-    <tableColumn id="4" name="Role"/>
-    <tableColumn id="5" name="Resolution [pix]"/>
-    <tableColumn id="6" name="MinLambda"/>
-    <tableColumn id="7" name="MaxLambda"/>
-    <tableColumn id="8" name="RefLambda"/>
+    <tableColumn id="3" name="ObservationSetID"/>
+    <tableColumn id="4" name="Resolution [pix]"/>
+    <tableColumn id="5" name="MinLambda"/>
+    <tableColumn id="6" name="MaxLambda"/>
+    <tableColumn id="7" name="RefLambda"/>
   </tableColumns>
 </table>
 </file>
@@ -1433,7 +1389,7 @@
   <tableColumns count="6">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Name"/>
-    <tableColumn id="3" name="Mode"/>
+    <tableColumn id="3" name="ObservationSetID"/>
     <tableColumn id="4" name="MinTargetSize"/>
     <tableColumn id="5" name="MaxTargetSize"/>
     <tableColumn id="6" name="RefTargetSize"/>
@@ -1646,7 +1602,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:XFD1048576"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="21" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="21" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.74"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26.44"/>
@@ -1711,38 +1667,36 @@
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="8"/>
+      <c r="B3" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="C3" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="D3" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="E3" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="F3" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="G3" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="H3" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="I3" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="J3" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="K3" s="9" t="s">
         <v>20</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>21</v>
       </c>
       <c r="L3" s="12"/>
       <c r="M3" s="12"/>
@@ -1793,34 +1747,34 @@
     <row r="4" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="8"/>
       <c r="B4" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="D4" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="9" t="s">
+      <c r="F4" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="F4" s="11" t="s">
-        <v>25</v>
-      </c>
       <c r="G4" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="I4" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="J4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="K4" s="9" t="s">
         <v>20</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>21</v>
       </c>
       <c r="L4" s="12"/>
       <c r="M4" s="12"/>
@@ -1871,34 +1825,34 @@
     <row r="5" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8"/>
       <c r="B5" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="D5" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="E5" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="F5" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="11" t="s">
-        <v>30</v>
-      </c>
       <c r="G5" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="H5" s="11" t="s">
+      <c r="I5" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="I5" s="11" t="s">
+      <c r="J5" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="J5" s="9" t="s">
+      <c r="K5" s="9" t="s">
         <v>20</v>
-      </c>
-      <c r="K5" s="9" t="s">
-        <v>21</v>
       </c>
       <c r="L5" s="12"/>
       <c r="M5" s="12"/>
@@ -1949,34 +1903,34 @@
     <row r="6" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8"/>
       <c r="B6" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="D6" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" s="9" t="s">
+      <c r="F6" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="11" t="s">
-        <v>34</v>
-      </c>
       <c r="G6" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="H6" s="11" t="s">
+      <c r="I6" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="I6" s="11" t="s">
+      <c r="J6" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="J6" s="9" t="s">
+      <c r="K6" s="9" t="s">
         <v>20</v>
-      </c>
-      <c r="K6" s="9" t="s">
-        <v>21</v>
       </c>
       <c r="L6" s="12"/>
       <c r="M6" s="12"/>
@@ -2027,34 +1981,34 @@
     <row r="7" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8"/>
       <c r="B7" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="D7" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>37</v>
-      </c>
       <c r="G7" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="H7" s="11" t="s">
+      <c r="I7" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="I7" s="11" t="s">
+      <c r="J7" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="J7" s="9" t="s">
+      <c r="K7" s="9" t="s">
         <v>20</v>
-      </c>
-      <c r="K7" s="9" t="s">
-        <v>21</v>
       </c>
       <c r="L7" s="12"/>
       <c r="M7" s="12"/>
@@ -2105,34 +2059,34 @@
     <row r="8" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8"/>
       <c r="B8" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="D8" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="D8" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>40</v>
-      </c>
       <c r="G8" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="H8" s="11" t="s">
+      <c r="I8" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="I8" s="11" t="s">
+      <c r="J8" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="J8" s="9" t="s">
+      <c r="K8" s="9" t="s">
         <v>20</v>
-      </c>
-      <c r="K8" s="9" t="s">
-        <v>21</v>
       </c>
       <c r="L8" s="12"/>
       <c r="M8" s="12"/>
@@ -2181,7 +2135,9 @@
       <c r="BD8" s="12"/>
     </row>
     <row r="9" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8"/>
+      <c r="A9" s="8" t="s">
+        <v>40</v>
+      </c>
       <c r="B9" s="9" t="s">
         <v>41</v>
       </c>
@@ -2189,28 +2145,28 @@
         <v>42</v>
       </c>
       <c r="D9" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>29</v>
       </c>
       <c r="F9" s="11" t="s">
         <v>43</v>
       </c>
       <c r="G9" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H9" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="H9" s="11" t="s">
+      <c r="I9" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="I9" s="11" t="s">
+      <c r="J9" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="J9" s="9" t="s">
+      <c r="K9" s="9" t="s">
         <v>20</v>
-      </c>
-      <c r="K9" s="9" t="s">
-        <v>21</v>
       </c>
       <c r="L9" s="12"/>
       <c r="M9" s="12"/>
@@ -2267,28 +2223,28 @@
         <v>45</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F10" s="11" t="s">
         <v>46</v>
       </c>
       <c r="G10" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H10" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="H10" s="11" t="s">
+      <c r="I10" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="I10" s="11" t="s">
+      <c r="J10" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="J10" s="9" t="s">
+      <c r="K10" s="9" t="s">
         <v>20</v>
-      </c>
-      <c r="K10" s="9" t="s">
-        <v>21</v>
       </c>
       <c r="L10" s="12"/>
       <c r="M10" s="12"/>
@@ -2367,291 +2323,115 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:XFD21"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:XFD16"/>
+  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="26.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="63.93"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="2" width="26.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="54.46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="30.03"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="68.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="26.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="2" width="30.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="2" width="26.66"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16381" min="12" style="2" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16382" style="3" width="10.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="2" width="29.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="40.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="29.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="40.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="29.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="40.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="2" width="29.34"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="12" min="12" style="12" width="11"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16383" min="13" style="2" width="11"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="19" t="s">
-        <v>235</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
+      <c r="A1" s="20" t="s">
+        <v>217</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="D2" s="20" t="s">
-        <v>199</v>
-      </c>
-      <c r="E2" s="20" t="s">
-        <v>273</v>
-      </c>
-      <c r="F2" s="20" t="s">
-        <v>274</v>
-      </c>
-      <c r="G2" s="20" t="s">
-        <v>275</v>
-      </c>
-      <c r="H2" s="20" t="s">
-        <v>276</v>
-      </c>
-      <c r="I2" s="20" t="s">
+      <c r="C2" s="21" t="s">
+        <v>264</v>
+      </c>
+      <c r="D2" s="21" t="s">
+        <v>265</v>
+      </c>
+      <c r="E2" s="21" t="s">
         <v>266</v>
       </c>
-      <c r="J2" s="20" t="s">
+      <c r="F2" s="21" t="s">
         <v>267</v>
       </c>
-      <c r="K2" s="20" t="s">
+      <c r="G2" s="21" t="s">
         <v>268</v>
       </c>
-      <c r="XFB2" s="3"/>
-      <c r="XFC2" s="3"/>
+      <c r="H2" s="21" t="s">
+        <v>269</v>
+      </c>
+      <c r="I2" s="21" t="s">
+        <v>246</v>
+      </c>
+      <c r="J2" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="K2" s="21" t="s">
+        <v>248</v>
+      </c>
+      <c r="L2" s="12"/>
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="21" t="s">
-        <v>146</v>
-      </c>
-      <c r="B3" s="21" t="s">
-        <v>277</v>
-      </c>
-      <c r="C3" s="21" t="s">
-        <v>278</v>
-      </c>
-      <c r="D3" s="21" t="s">
-        <v>279</v>
-      </c>
-      <c r="E3" s="21" t="s">
-        <v>280</v>
-      </c>
-      <c r="F3" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="G3" s="21" t="b">
+      <c r="A3" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>270</v>
+      </c>
+      <c r="C3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H3" s="21" t="s">
-        <v>282</v>
-      </c>
-      <c r="I3" s="21" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J3" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="K3" s="21" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="21" t="s">
-        <v>152</v>
-      </c>
-      <c r="B4" s="21" t="s">
-        <v>283</v>
-      </c>
-      <c r="C4" s="21" t="s">
-        <v>278</v>
-      </c>
-      <c r="D4" s="21" t="s">
-        <v>205</v>
-      </c>
-      <c r="E4" s="21" t="s">
-        <v>280</v>
-      </c>
-      <c r="F4" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="G4" s="21" t="b">
+      <c r="D3" s="22" t="s">
+        <v>271</v>
+      </c>
+      <c r="E3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H4" s="21" t="s">
-        <v>282</v>
-      </c>
-      <c r="I4" s="21" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J4" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="K4" s="21" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="21" t="s">
-        <v>167</v>
-      </c>
-      <c r="B5" s="21" t="s">
-        <v>284</v>
-      </c>
-      <c r="C5" s="21" t="s">
-        <v>278</v>
-      </c>
-      <c r="D5" s="21" t="s">
-        <v>279</v>
-      </c>
-      <c r="E5" s="21" t="s">
-        <v>280</v>
-      </c>
-      <c r="F5" s="21" t="s">
-        <v>285</v>
-      </c>
-      <c r="G5" s="21" t="b">
+      <c r="F3" s="22" t="s">
+        <v>272</v>
+      </c>
+      <c r="G3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H5" s="21" t="s">
-        <v>286</v>
-      </c>
-      <c r="I5" s="21" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J5" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="K5" s="21" t="n">
+      <c r="H3" s="22" t="s">
+        <v>273</v>
+      </c>
+      <c r="I3" s="22" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J3" s="22" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="21" t="s">
-        <v>170</v>
-      </c>
-      <c r="B6" s="21" t="s">
-        <v>287</v>
-      </c>
-      <c r="C6" s="21" t="s">
-        <v>278</v>
-      </c>
-      <c r="D6" s="21" t="s">
-        <v>205</v>
-      </c>
-      <c r="E6" s="21" t="s">
-        <v>280</v>
-      </c>
-      <c r="F6" s="21" t="s">
-        <v>285</v>
-      </c>
-      <c r="G6" s="21" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="H6" s="21" t="s">
-        <v>286</v>
-      </c>
-      <c r="I6" s="21" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J6" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" s="21" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="21" t="s">
-        <v>191</v>
-      </c>
-      <c r="B7" s="21" t="s">
-        <v>288</v>
-      </c>
-      <c r="C7" s="21" t="s">
-        <v>278</v>
-      </c>
-      <c r="D7" s="21" t="s">
-        <v>289</v>
-      </c>
-      <c r="E7" s="21" t="s">
-        <v>280</v>
-      </c>
-      <c r="F7" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="G7" s="21" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="H7" s="21" t="s">
-        <v>282</v>
-      </c>
-      <c r="I7" s="21" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J7" s="21" t="n">
-        <v>3</v>
-      </c>
-      <c r="K7" s="21" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="21" t="s">
-        <v>196</v>
-      </c>
-      <c r="B8" s="21" t="s">
-        <v>290</v>
-      </c>
-      <c r="C8" s="21" t="s">
-        <v>278</v>
-      </c>
-      <c r="D8" s="21" t="s">
-        <v>289</v>
-      </c>
-      <c r="E8" s="21" t="s">
-        <v>280</v>
-      </c>
-      <c r="F8" s="21" t="s">
-        <v>285</v>
-      </c>
-      <c r="G8" s="21" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="H8" s="21" t="s">
-        <v>286</v>
-      </c>
-      <c r="I8" s="21" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J8" s="21" t="n">
-        <v>3</v>
-      </c>
-      <c r="K8" s="21" t="n">
-        <v>6</v>
-      </c>
-    </row>
+      <c r="K3" s="22" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="5" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="6" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="7" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="8" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="9" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2660,11 +2440,6 @@
     <row r="14" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="15" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="16" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="17" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="18" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="19" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="20" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="21" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:K1"/>
@@ -2688,7 +2463,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:XFD1048576"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="26.78"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="33.54"/>
@@ -2728,7 +2503,7 @@
     </row>
     <row r="3" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>49</v>
@@ -2742,7 +2517,7 @@
     </row>
     <row r="4" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>52</v>
@@ -2779,7 +2554,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:BM1048576"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="26.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="38.38"/>
@@ -2889,7 +2664,7 @@
         <v>59</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>60</v>
@@ -2970,7 +2745,7 @@
         <v>64</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>60</v>
@@ -3051,7 +2826,7 @@
         <v>67</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D5" s="9" t="s">
         <v>60</v>
@@ -3132,7 +2907,7 @@
         <v>70</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D6" s="9" t="s">
         <v>60</v>
@@ -3231,21 +3006,22 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:XFD1048576"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="26.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="12" width="38.28"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="26.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="12" width="26.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="26.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="29.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="36.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="2" width="26.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="2" width="29.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="2" width="26.66"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="18" min="14" style="12" width="11"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16381" min="19" style="2" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16382" style="2" width="10.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="12" width="26.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="26.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="29.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="36.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="2" width="26.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="2" width="29.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="2" width="26.66"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16" min="12" style="12" width="11"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16379" min="17" style="2" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16382" min="16380" style="0" width="10.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16383" style="2" width="10.49"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3261,9 +3037,6 @@
       <c r="H1" s="16"/>
       <c r="I1" s="16"/>
       <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="XFB1" s="3"/>
       <c r="XFC1" s="3"/>
       <c r="XFD1" s="3"/>
     </row>
@@ -3298,328 +3071,272 @@
       <c r="J2" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="K2" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="L2" s="17" t="s">
-        <v>81</v>
-      </c>
+      <c r="L2" s="12"/>
+      <c r="M2" s="12"/>
       <c r="N2" s="12"/>
       <c r="O2" s="12"/>
       <c r="P2" s="12"/>
-      <c r="Q2" s="12"/>
-      <c r="R2" s="12"/>
-      <c r="XFB2" s="3"/>
+      <c r="XEZ2" s="0"/>
+      <c r="XFA2" s="0"/>
+      <c r="XFB2" s="0"/>
       <c r="XFC2" s="3"/>
       <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="E3" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="C3" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="18" t="s">
+      <c r="F3" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="G3" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="F3" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="G3" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="H3" s="18" t="s">
-        <v>88</v>
-      </c>
-      <c r="I3" s="18" t="s">
-        <v>89</v>
+      <c r="H3" s="18" t="n">
+        <v>300</v>
+      </c>
+      <c r="I3" s="18" t="n">
+        <v>3</v>
       </c>
       <c r="J3" s="18" t="n">
-        <v>300</v>
-      </c>
-      <c r="K3" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="L3" s="18" t="n">
         <v>12000</v>
       </c>
-      <c r="XFB3" s="3"/>
       <c r="XFC3" s="3"/>
       <c r="XFD3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="18" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D4" s="18" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E4" s="18" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="F4" s="18" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G4" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="H4" s="18" t="s">
-        <v>88</v>
-      </c>
-      <c r="I4" s="18" t="s">
-        <v>89</v>
+        <v>85</v>
+      </c>
+      <c r="H4" s="18" t="n">
+        <v>300</v>
+      </c>
+      <c r="I4" s="18" t="n">
+        <v>3</v>
       </c>
       <c r="J4" s="18" t="n">
-        <v>300</v>
-      </c>
-      <c r="K4" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="L4" s="18" t="n">
         <v>12000</v>
       </c>
-      <c r="XFB4" s="3"/>
-      <c r="XFC4" s="3"/>
-      <c r="XFD4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="18" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E5" s="18" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="F5" s="18" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G5" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="H5" s="18" t="s">
-        <v>88</v>
-      </c>
-      <c r="I5" s="18" t="s">
-        <v>89</v>
+        <v>85</v>
+      </c>
+      <c r="H5" s="18" t="n">
+        <v>300</v>
+      </c>
+      <c r="I5" s="18" t="n">
+        <v>3</v>
       </c>
       <c r="J5" s="18" t="n">
-        <v>300</v>
-      </c>
-      <c r="K5" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="L5" s="18" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="E6" s="18" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="F6" s="18" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G6" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="H6" s="18" t="s">
-        <v>88</v>
-      </c>
-      <c r="I6" s="18" t="s">
-        <v>89</v>
+        <v>85</v>
+      </c>
+      <c r="H6" s="18" t="n">
+        <v>300</v>
+      </c>
+      <c r="I6" s="18" t="n">
+        <v>3</v>
       </c>
       <c r="J6" s="18" t="n">
-        <v>300</v>
-      </c>
-      <c r="K6" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="L6" s="18" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="E7" s="18" t="s">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="F7" s="18" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="G7" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="H7" s="18" t="s">
-        <v>88</v>
-      </c>
-      <c r="I7" s="18" t="s">
-        <v>89</v>
+        <v>85</v>
+      </c>
+      <c r="H7" s="18" t="n">
+        <v>300</v>
+      </c>
+      <c r="I7" s="18" t="n">
+        <v>3</v>
       </c>
       <c r="J7" s="18" t="n">
-        <v>300</v>
-      </c>
-      <c r="K7" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="L7" s="18" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="18" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="E8" s="18" t="s">
-        <v>111</v>
+        <v>83</v>
       </c>
       <c r="F8" s="18" t="s">
-        <v>112</v>
+        <v>84</v>
       </c>
       <c r="G8" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="H8" s="18" t="s">
-        <v>88</v>
-      </c>
-      <c r="I8" s="18" t="s">
-        <v>89</v>
+        <v>85</v>
+      </c>
+      <c r="H8" s="18" t="n">
+        <v>300</v>
+      </c>
+      <c r="I8" s="18" t="n">
+        <v>3</v>
       </c>
       <c r="J8" s="18" t="n">
-        <v>300</v>
-      </c>
-      <c r="K8" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="L8" s="18" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="18" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="C9" s="18" t="s">
         <v>43</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
       <c r="F9" s="18" t="s">
-        <v>117</v>
+        <v>84</v>
       </c>
       <c r="G9" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="H9" s="18" t="s">
-        <v>88</v>
-      </c>
-      <c r="I9" s="18" t="s">
-        <v>89</v>
+        <v>85</v>
+      </c>
+      <c r="H9" s="18" t="n">
+        <v>300</v>
+      </c>
+      <c r="I9" s="18" t="n">
+        <v>3</v>
       </c>
       <c r="J9" s="18" t="n">
-        <v>300</v>
-      </c>
-      <c r="K9" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="L9" s="18" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="18" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="C10" s="18" t="s">
         <v>46</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>121</v>
+        <v>92</v>
       </c>
       <c r="F10" s="18" t="s">
-        <v>122</v>
+        <v>84</v>
       </c>
       <c r="G10" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="H10" s="18" t="s">
-        <v>88</v>
-      </c>
-      <c r="I10" s="18" t="s">
-        <v>89</v>
+        <v>85</v>
+      </c>
+      <c r="H10" s="18" t="n">
+        <v>300</v>
+      </c>
+      <c r="I10" s="18" t="n">
+        <v>3</v>
       </c>
       <c r="J10" s="18" t="n">
-        <v>300</v>
-      </c>
-      <c r="K10" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="L10" s="18" t="n">
         <v>12000</v>
       </c>
     </row>
@@ -3632,12 +3349,10 @@
     <row r="17" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="18" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="19" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A1:J1"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3658,7 +3373,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:XFD23"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="26.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="12" width="38.28"/>
@@ -3669,7 +3384,8 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="12" min="8" style="12" width="11"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16375" min="13" style="2" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16378" min="16376" style="2" width="10.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16379" style="3" width="10.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16379" min="16379" style="0" width="10.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16380" style="12" width="10.49"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3690,38 +3406,38 @@
         <v>2</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="H2" s="12"/>
       <c r="I2" s="12"/>
       <c r="J2" s="12"/>
       <c r="K2" s="12"/>
       <c r="L2" s="12"/>
-      <c r="XEY2" s="3"/>
-      <c r="XEZ2" s="3"/>
-      <c r="XFA2" s="3"/>
-      <c r="XFB2" s="3"/>
-      <c r="XFC2" s="3"/>
-      <c r="XFD2" s="3"/>
-    </row>
-    <row r="3" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="XEY2" s="0"/>
+      <c r="XEZ2" s="12"/>
+      <c r="XFA2" s="12"/>
+      <c r="XFB2" s="12"/>
+      <c r="XFC2" s="12"/>
+      <c r="XFD2" s="12"/>
+    </row>
+    <row r="3" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="18" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="D3" s="18" t="n">
         <v>0.2</v>
@@ -3733,26 +3449,20 @@
         <v>0.8</v>
       </c>
       <c r="G3" s="2"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
-      <c r="L3" s="12"/>
-      <c r="M3" s="12"/>
-      <c r="N3" s="12"/>
       <c r="XEV3" s="2"/>
       <c r="XEW3" s="2"/>
       <c r="XEX3" s="2"/>
-    </row>
-    <row r="4" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="XEY3" s="0"/>
+    </row>
+    <row r="4" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="18" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="D4" s="18" t="n">
         <v>0.2</v>
@@ -3764,26 +3474,20 @@
         <v>0.8</v>
       </c>
       <c r="G4" s="2"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="12"/>
-      <c r="K4" s="12"/>
-      <c r="L4" s="12"/>
-      <c r="M4" s="12"/>
-      <c r="N4" s="12"/>
       <c r="XEV4" s="2"/>
       <c r="XEW4" s="2"/>
       <c r="XEX4" s="2"/>
-    </row>
-    <row r="5" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="XEY4" s="0"/>
+    </row>
+    <row r="5" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="18" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="D5" s="18" t="n">
         <v>0.2</v>
@@ -3795,26 +3499,20 @@
         <v>0.8</v>
       </c>
       <c r="G5" s="2"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="12"/>
-      <c r="L5" s="12"/>
-      <c r="M5" s="12"/>
-      <c r="N5" s="12"/>
       <c r="XEV5" s="2"/>
       <c r="XEW5" s="2"/>
       <c r="XEX5" s="2"/>
-    </row>
-    <row r="6" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="XEY5" s="0"/>
+    </row>
+    <row r="6" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="D6" s="18" t="n">
         <v>0.2</v>
@@ -3826,26 +3524,20 @@
         <v>0.8</v>
       </c>
       <c r="G6" s="2"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="12"/>
-      <c r="N6" s="12"/>
       <c r="XEV6" s="2"/>
       <c r="XEW6" s="2"/>
       <c r="XEX6" s="2"/>
-    </row>
-    <row r="7" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="XEY6" s="0"/>
+    </row>
+    <row r="7" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="D7" s="18" t="n">
         <v>0.2</v>
@@ -3857,26 +3549,20 @@
         <v>0.8</v>
       </c>
       <c r="G7" s="2"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="12"/>
-      <c r="J7" s="12"/>
-      <c r="K7" s="12"/>
-      <c r="L7" s="12"/>
-      <c r="M7" s="12"/>
-      <c r="N7" s="12"/>
       <c r="XEV7" s="2"/>
       <c r="XEW7" s="2"/>
       <c r="XEX7" s="2"/>
-    </row>
-    <row r="8" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="XEY7" s="0"/>
+    </row>
+    <row r="8" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="18" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D8" s="18" t="n">
         <v>0.2</v>
@@ -3888,26 +3574,20 @@
         <v>0.8</v>
       </c>
       <c r="G8" s="2"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="12"/>
-      <c r="K8" s="12"/>
-      <c r="L8" s="12"/>
-      <c r="M8" s="12"/>
-      <c r="N8" s="12"/>
       <c r="XEV8" s="2"/>
       <c r="XEW8" s="2"/>
       <c r="XEX8" s="2"/>
-    </row>
-    <row r="9" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="XEY8" s="0"/>
+    </row>
+    <row r="9" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="18" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="D9" s="18" t="n">
         <v>0.2</v>
@@ -3919,26 +3599,20 @@
         <v>0.8</v>
       </c>
       <c r="G9" s="2"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12"/>
-      <c r="K9" s="12"/>
-      <c r="L9" s="12"/>
-      <c r="M9" s="12"/>
-      <c r="N9" s="12"/>
       <c r="XEV9" s="2"/>
       <c r="XEW9" s="2"/>
       <c r="XEX9" s="2"/>
-    </row>
-    <row r="10" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="XEY9" s="0"/>
+    </row>
+    <row r="10" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="18" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D10" s="18" t="n">
         <v>0.2</v>
@@ -3950,16 +3624,10 @@
         <v>0.8</v>
       </c>
       <c r="G10" s="2"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="12"/>
-      <c r="L10" s="12"/>
-      <c r="M10" s="12"/>
-      <c r="N10" s="12"/>
       <c r="XEV10" s="2"/>
       <c r="XEW10" s="2"/>
       <c r="XEX10" s="2"/>
+      <c r="XEY10" s="0"/>
     </row>
     <row r="11" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="12" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -3997,7 +3665,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:XFD1048576"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="27.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="45.28"/>
@@ -4005,9 +3673,9 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="12" width="27.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="36.2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="2" width="27.34"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="13" min="13" style="12" width="11"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="14" min="12" style="12" width="11"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16383" min="15" style="2" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="3" width="10.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="0" width="10.49"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4033,61 +3701,61 @@
       <c r="B2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="17" t="s">
-        <v>74</v>
+      <c r="C2" s="19" t="s">
+        <v>108</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="G2" s="17" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H2" s="17" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I2" s="17" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="J2" s="17" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="K2" s="17" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="M2" s="12"/>
-      <c r="N2" s="3"/>
-      <c r="XFD2" s="3"/>
+      <c r="N2" s="12"/>
+      <c r="XFD2" s="0"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="18" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>85</v>
+        <v>113</v>
       </c>
       <c r="D3" s="18" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="E3" s="18" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="F3" s="18" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="G3" s="18" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="H3" s="18" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I3" s="18" t="n">
         <v>3</v>
@@ -4102,28 +3770,28 @@
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="18" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>85</v>
+        <v>113</v>
       </c>
       <c r="D4" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="E4" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="F4" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="G4" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="E4" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="F4" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="G4" s="18" t="s">
-        <v>154</v>
-      </c>
       <c r="H4" s="18" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="I4" s="18" t="n">
         <v>8</v>
@@ -4138,28 +3806,28 @@
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="18" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>85</v>
+        <v>113</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E5" s="18" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="F5" s="18" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="G5" s="18" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="H5" s="18" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I5" s="18" t="n">
         <v>8</v>
@@ -4174,28 +3842,28 @@
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="E6" s="18" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="F6" s="18" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="G6" s="18" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="H6" s="18" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I6" s="18" t="n">
         <v>3</v>
@@ -4210,28 +3878,28 @@
     </row>
     <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="D7" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="G7" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="E7" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="F7" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="G7" s="18" t="s">
-        <v>154</v>
-      </c>
       <c r="H7" s="18" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="I7" s="18" t="n">
         <v>8</v>
@@ -4246,28 +3914,28 @@
     </row>
     <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="18" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E8" s="18" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="F8" s="18" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="G8" s="18" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="H8" s="18" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I8" s="18" t="n">
         <v>8</v>
@@ -4282,28 +3950,28 @@
     </row>
     <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="18" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="F9" s="18" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="G9" s="18" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="H9" s="18" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I9" s="18" t="n">
         <v>3</v>
@@ -4318,28 +3986,28 @@
     </row>
     <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="18" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="D10" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="F10" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="G10" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="E10" s="18" t="s">
-        <v>170</v>
-      </c>
-      <c r="F10" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="G10" s="18" t="s">
-        <v>154</v>
-      </c>
       <c r="H10" s="18" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="I10" s="18" t="n">
         <v>8</v>
@@ -4354,28 +4022,28 @@
     </row>
     <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="18" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="E11" s="18" t="s">
-        <v>170</v>
+        <v>137</v>
       </c>
       <c r="F11" s="18" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="G11" s="18" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="H11" s="18" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I11" s="18" t="n">
         <v>8</v>
@@ -4390,28 +4058,28 @@
     </row>
     <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="18" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="D12" s="18" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="E12" s="18" t="s">
-        <v>170</v>
+        <v>137</v>
       </c>
       <c r="F12" s="18" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="G12" s="18" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="H12" s="18" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="I12" s="18" t="n">
         <v>8</v>
@@ -4426,28 +4094,28 @@
     </row>
     <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="18" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="E13" s="18" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="F13" s="18" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="G13" s="18" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="H13" s="18" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I13" s="18" t="n">
         <v>3</v>
@@ -4462,28 +4130,28 @@
     </row>
     <row r="14" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="18" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="D14" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="F14" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="G14" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="E14" s="18" t="s">
-        <v>170</v>
-      </c>
-      <c r="F14" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="G14" s="18" t="s">
-        <v>154</v>
-      </c>
       <c r="H14" s="18" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="I14" s="18" t="n">
         <v>8</v>
@@ -4498,28 +4166,28 @@
     </row>
     <row r="15" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="18" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>170</v>
+        <v>137</v>
       </c>
       <c r="F15" s="18" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="G15" s="18" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="H15" s="18" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I15" s="18" t="n">
         <v>8</v>
@@ -4534,28 +4202,28 @@
     </row>
     <row r="16" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="18" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="E16" s="18" t="s">
-        <v>170</v>
+        <v>137</v>
       </c>
       <c r="F16" s="18" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="G16" s="18" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="H16" s="18" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="I16" s="18" t="n">
         <v>8</v>
@@ -4570,28 +4238,28 @@
     </row>
     <row r="17" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="18" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="E17" s="18" t="s">
-        <v>170</v>
+        <v>137</v>
       </c>
       <c r="F17" s="18" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="G17" s="18" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="H17" s="18" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="I17" s="18" t="n">
         <v>8</v>
@@ -4604,30 +4272,30 @@
       </c>
       <c r="L17" s="2"/>
     </row>
-    <row r="18" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="18" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="D18" s="18" t="s">
-        <v>145</v>
+        <v>182</v>
       </c>
       <c r="E18" s="18" t="s">
-        <v>191</v>
+        <v>137</v>
       </c>
       <c r="F18" s="18" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="G18" s="18" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="H18" s="18" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I18" s="18" t="n">
         <v>3</v>
@@ -4639,32 +4307,32 @@
         <v>3</v>
       </c>
       <c r="L18" s="2"/>
-      <c r="M18" s="12"/>
-    </row>
-    <row r="19" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="XFD18" s="0"/>
+    </row>
+    <row r="19" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="18" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="C19" s="18" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="D19" s="18" t="s">
-        <v>145</v>
+        <v>182</v>
       </c>
       <c r="E19" s="18" t="s">
-        <v>191</v>
+        <v>137</v>
       </c>
       <c r="F19" s="18" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="G19" s="18" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="H19" s="18" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I19" s="18" t="n">
         <v>3</v>
@@ -4676,32 +4344,32 @@
         <v>3</v>
       </c>
       <c r="L19" s="2"/>
-      <c r="M19" s="12"/>
-    </row>
-    <row r="20" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="XFD19" s="0"/>
+    </row>
+    <row r="20" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="18" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="D20" s="18" t="s">
-        <v>145</v>
+        <v>187</v>
       </c>
       <c r="E20" s="18" t="s">
-        <v>196</v>
+        <v>137</v>
       </c>
       <c r="F20" s="18" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="G20" s="18" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="H20" s="18" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I20" s="18" t="n">
         <v>3</v>
@@ -4713,32 +4381,32 @@
         <v>3</v>
       </c>
       <c r="L20" s="2"/>
-      <c r="M20" s="12"/>
-    </row>
-    <row r="21" s="3" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="XFD20" s="0"/>
+    </row>
+    <row r="21" s="12" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="18" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>145</v>
+        <v>187</v>
       </c>
       <c r="E21" s="18" t="s">
-        <v>196</v>
+        <v>137</v>
       </c>
       <c r="F21" s="18" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="G21" s="18" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="H21" s="18" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="I21" s="18" t="n">
         <v>3</v>
@@ -4750,7 +4418,7 @@
         <v>3</v>
       </c>
       <c r="L21" s="2"/>
-      <c r="M21" s="12"/>
+      <c r="XFD21" s="0"/>
     </row>
     <row r="22" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="23" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -4766,11 +4434,7 @@
     <row r="33" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="34" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="35" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
@@ -4794,15 +4458,16 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:XFD1048576"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="27.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="45.28"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="27.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="12" width="27.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="2" width="27.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="12" width="27.34"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16376" min="9" style="2" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="12" width="27.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="2" width="27.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="12" width="27.34"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16375" min="8" style="2" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16376" min="16376" style="0" width="10.49"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16377" style="3" width="10.49"/>
   </cols>
   <sheetData>
@@ -4816,7 +4481,6 @@
       <c r="E1" s="16"/>
       <c r="F1" s="16"/>
       <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="17" t="s">
@@ -4825,24 +4489,22 @@
       <c r="B2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="17" t="s">
-        <v>75</v>
+      <c r="C2" s="19" t="s">
+        <v>108</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>139</v>
+        <v>190</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="G2" s="17" t="s">
-        <v>201</v>
-      </c>
-      <c r="H2" s="17" t="s">
-        <v>202</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="XEV2" s="0"/>
       <c r="XEW2" s="3"/>
       <c r="XEX2" s="3"/>
       <c r="XEY2" s="3"/>
@@ -4854,394 +4516,261 @@
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="18" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="D3" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="E3" s="18" t="s">
-        <v>205</v>
+        <v>196</v>
+      </c>
+      <c r="E3" s="18" t="n">
+        <v>0.167</v>
       </c>
       <c r="F3" s="18" t="n">
-        <v>0.167</v>
+        <v>1</v>
       </c>
       <c r="G3" s="18" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="H3" s="18" t="n">
-        <v>0.167</v>
+        <v>0.583</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="18" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="D4" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="E4" s="18" t="s">
-        <v>208</v>
+        <v>196</v>
+      </c>
+      <c r="E4" s="18" t="n">
+        <v>0.167</v>
       </c>
       <c r="F4" s="18" t="n">
-        <v>0.167</v>
+        <v>1</v>
       </c>
       <c r="G4" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" s="18" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="18" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="E5" s="18" t="s">
-        <v>208</v>
+        <v>196</v>
+      </c>
+      <c r="E5" s="18" t="n">
+        <v>0.167</v>
       </c>
       <c r="F5" s="18" t="n">
-        <v>0.167</v>
+        <v>1</v>
       </c>
       <c r="G5" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="18" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="E6" s="18" t="s">
-        <v>205</v>
+        <v>196</v>
+      </c>
+      <c r="E6" s="18" t="n">
+        <v>0.167</v>
       </c>
       <c r="F6" s="18" t="n">
-        <v>0.167</v>
+        <v>1</v>
       </c>
       <c r="G6" s="18" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="H6" s="18" t="n">
-        <v>0.167</v>
+        <v>0.583</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="E7" s="18" t="s">
-        <v>208</v>
+        <v>196</v>
+      </c>
+      <c r="E7" s="18" t="n">
+        <v>0.167</v>
       </c>
       <c r="F7" s="18" t="n">
-        <v>0.167</v>
+        <v>1</v>
       </c>
       <c r="G7" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="18" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="18" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="E8" s="18" t="s">
-        <v>208</v>
+        <v>196</v>
+      </c>
+      <c r="E8" s="18" t="n">
+        <v>0.167</v>
       </c>
       <c r="F8" s="18" t="n">
-        <v>0.167</v>
+        <v>1</v>
       </c>
       <c r="G8" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="18" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="18" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="E9" s="18" t="s">
-        <v>205</v>
+        <v>196</v>
+      </c>
+      <c r="E9" s="18" t="n">
+        <v>0.167</v>
       </c>
       <c r="F9" s="18" t="n">
-        <v>0.167</v>
+        <v>1</v>
       </c>
       <c r="G9" s="18" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="H9" s="18" t="n">
-        <v>0.167</v>
+        <v>0.583</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="18" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="E10" s="18" t="s">
-        <v>208</v>
+        <v>196</v>
+      </c>
+      <c r="E10" s="18" t="n">
+        <v>0.167</v>
       </c>
       <c r="F10" s="18" t="n">
-        <v>0.167</v>
+        <v>1</v>
       </c>
       <c r="G10" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="18" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="18" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="E11" s="18" t="s">
-        <v>208</v>
+        <v>196</v>
+      </c>
+      <c r="E11" s="18" t="n">
+        <v>0.167</v>
       </c>
       <c r="F11" s="18" t="n">
-        <v>0.167</v>
+        <v>1</v>
       </c>
       <c r="G11" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="18" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="18" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="D12" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="E12" s="18" t="s">
-        <v>208</v>
+        <v>196</v>
+      </c>
+      <c r="E12" s="18" t="n">
+        <v>0.167</v>
       </c>
       <c r="F12" s="18" t="n">
-        <v>0.167</v>
+        <v>1</v>
       </c>
       <c r="G12" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="18" t="n">
         <v>0.583</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="18" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="E13" s="18" t="s">
-        <v>205</v>
+        <v>196</v>
+      </c>
+      <c r="E13" s="18" t="n">
+        <v>0.167</v>
       </c>
       <c r="F13" s="18" t="n">
-        <v>0.167</v>
+        <v>1</v>
       </c>
       <c r="G13" s="18" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="H13" s="18" t="n">
-        <v>0.167</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="18" t="s">
-        <v>227</v>
-      </c>
-      <c r="B14" s="18" t="s">
-        <v>228</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>122</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="E14" s="18" t="s">
-        <v>208</v>
-      </c>
-      <c r="F14" s="18" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="G14" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="18" t="n">
         <v>0.583</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="18" t="s">
-        <v>229</v>
-      </c>
-      <c r="B15" s="18" t="s">
-        <v>230</v>
-      </c>
-      <c r="C15" s="18" t="s">
-        <v>122</v>
-      </c>
-      <c r="D15" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="E15" s="18" t="s">
-        <v>208</v>
-      </c>
-      <c r="F15" s="18" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="G15" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" s="18" t="n">
-        <v>0.583</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="18" t="s">
-        <v>231</v>
-      </c>
-      <c r="B16" s="18" t="s">
-        <v>232</v>
-      </c>
-      <c r="C16" s="18" t="s">
-        <v>122</v>
-      </c>
-      <c r="D16" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="E16" s="18" t="s">
-        <v>208</v>
-      </c>
-      <c r="F16" s="18" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="G16" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" s="18" t="n">
-        <v>0.583</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="18" t="s">
-        <v>233</v>
-      </c>
-      <c r="B17" s="18" t="s">
-        <v>234</v>
-      </c>
-      <c r="C17" s="18" t="s">
-        <v>122</v>
-      </c>
-      <c r="D17" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="E17" s="18" t="s">
-        <v>208</v>
-      </c>
-      <c r="F17" s="18" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="G17" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" s="18" t="n">
-        <v>0.583</v>
-      </c>
-    </row>
+    <row r="14" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="17" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="18" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="19" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="20" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -5251,17 +4780,10 @@
     <row r="24" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="25" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="26" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="27" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="28" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="29" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="30" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -5282,7 +4804,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:R1048576"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="2" width="26.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="34.64"/>
@@ -5300,200 +4822,200 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="19" t="s">
-        <v>235</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
-      <c r="O1" s="19"/>
-      <c r="P1" s="19"/>
-      <c r="Q1" s="19"/>
-      <c r="R1" s="19"/>
+      <c r="A1" s="20" t="s">
+        <v>217</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
+      <c r="R1" s="20"/>
     </row>
     <row r="2" customFormat="false" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="D2" s="20" t="s">
-        <v>236</v>
-      </c>
-      <c r="E2" s="20" t="s">
-        <v>237</v>
-      </c>
-      <c r="F2" s="20" t="s">
-        <v>238</v>
-      </c>
-      <c r="G2" s="20" t="s">
-        <v>239</v>
-      </c>
-      <c r="H2" s="20" t="s">
-        <v>240</v>
-      </c>
-      <c r="I2" s="20" t="s">
-        <v>241</v>
-      </c>
-      <c r="J2" s="20" t="s">
-        <v>242</v>
-      </c>
-      <c r="K2" s="20" t="s">
-        <v>243</v>
-      </c>
-      <c r="L2" s="20" t="s">
-        <v>244</v>
-      </c>
-      <c r="M2" s="20" t="s">
-        <v>245</v>
-      </c>
-      <c r="N2" s="20" t="s">
-        <v>246</v>
-      </c>
-      <c r="O2" s="20" t="s">
-        <v>247</v>
-      </c>
-      <c r="P2" s="20" t="s">
-        <v>248</v>
-      </c>
-      <c r="Q2" s="20" t="s">
-        <v>249</v>
-      </c>
-      <c r="R2" s="20" t="s">
-        <v>250</v>
+      <c r="D2" s="21" t="s">
+        <v>218</v>
+      </c>
+      <c r="E2" s="21" t="s">
+        <v>219</v>
+      </c>
+      <c r="F2" s="21" t="s">
+        <v>220</v>
+      </c>
+      <c r="G2" s="21" t="s">
+        <v>221</v>
+      </c>
+      <c r="H2" s="21" t="s">
+        <v>222</v>
+      </c>
+      <c r="I2" s="21" t="s">
+        <v>223</v>
+      </c>
+      <c r="J2" s="21" t="s">
+        <v>224</v>
+      </c>
+      <c r="K2" s="21" t="s">
+        <v>225</v>
+      </c>
+      <c r="L2" s="21" t="s">
+        <v>226</v>
+      </c>
+      <c r="M2" s="21" t="s">
+        <v>227</v>
+      </c>
+      <c r="N2" s="21" t="s">
+        <v>228</v>
+      </c>
+      <c r="O2" s="21" t="s">
+        <v>229</v>
+      </c>
+      <c r="P2" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="Q2" s="21" t="s">
+        <v>231</v>
+      </c>
+      <c r="R2" s="21" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="21" t="s">
-        <v>87</v>
-      </c>
-      <c r="B3" s="21" t="s">
+      <c r="A3" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="B3" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="C3" s="21" t="s">
-        <v>251</v>
-      </c>
-      <c r="D3" s="21" t="n">
+      <c r="C3" s="22" t="s">
+        <v>233</v>
+      </c>
+      <c r="D3" s="22" t="n">
         <v>8</v>
       </c>
-      <c r="E3" s="21" t="n">
+      <c r="E3" s="22" t="n">
         <v>12</v>
       </c>
-      <c r="F3" s="21" t="b">
+      <c r="F3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="G3" s="21" t="s">
-        <v>252</v>
-      </c>
-      <c r="H3" s="21" t="b">
+      <c r="G3" s="22" t="s">
+        <v>234</v>
+      </c>
+      <c r="H3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="I3" s="21" t="s">
-        <v>253</v>
-      </c>
-      <c r="J3" s="21" t="b">
+      <c r="I3" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="J3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="K3" s="21" t="s">
-        <v>254</v>
-      </c>
-      <c r="L3" s="21" t="b">
+      <c r="K3" s="22" t="s">
+        <v>236</v>
+      </c>
+      <c r="L3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="M3" s="21" t="s">
-        <v>255</v>
-      </c>
-      <c r="N3" s="21" t="n">
+      <c r="M3" s="22" t="s">
+        <v>237</v>
+      </c>
+      <c r="N3" s="22" t="n">
         <v>6.5</v>
       </c>
-      <c r="O3" s="21" t="n">
+      <c r="O3" s="22" t="n">
         <v>2.5</v>
       </c>
-      <c r="P3" s="21" t="n">
+      <c r="P3" s="22" t="n">
         <v>400</v>
       </c>
-      <c r="Q3" s="21" t="n">
+      <c r="Q3" s="22" t="n">
         <v>350</v>
       </c>
-      <c r="R3" s="21" t="n">
+      <c r="R3" s="22" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="21" t="s">
-        <v>98</v>
-      </c>
-      <c r="B4" s="21" t="s">
+      <c r="A4" s="22" t="s">
+        <v>92</v>
+      </c>
+      <c r="B4" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="21" t="s">
-        <v>251</v>
-      </c>
-      <c r="D4" s="21" t="n">
+      <c r="C4" s="22" t="s">
+        <v>233</v>
+      </c>
+      <c r="D4" s="22" t="n">
         <v>8</v>
       </c>
-      <c r="E4" s="21" t="n">
+      <c r="E4" s="22" t="n">
         <v>12</v>
       </c>
-      <c r="F4" s="21" t="b">
+      <c r="F4" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="G4" s="21" t="s">
-        <v>256</v>
-      </c>
-      <c r="H4" s="21" t="b">
+      <c r="G4" s="22" t="s">
+        <v>238</v>
+      </c>
+      <c r="H4" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="I4" s="21" t="s">
-        <v>257</v>
-      </c>
-      <c r="J4" s="21" t="b">
+      <c r="I4" s="22" t="s">
+        <v>239</v>
+      </c>
+      <c r="J4" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="K4" s="21" t="s">
-        <v>258</v>
-      </c>
-      <c r="L4" s="21" t="b">
+      <c r="K4" s="22" t="s">
+        <v>240</v>
+      </c>
+      <c r="L4" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="M4" s="21" t="s">
-        <v>259</v>
-      </c>
-      <c r="N4" s="21" t="n">
+      <c r="M4" s="22" t="s">
+        <v>241</v>
+      </c>
+      <c r="N4" s="22" t="n">
         <v>6.5</v>
       </c>
-      <c r="O4" s="21" t="n">
+      <c r="O4" s="22" t="n">
         <v>2.5</v>
       </c>
-      <c r="P4" s="21" t="n">
+      <c r="P4" s="22" t="n">
         <v>400</v>
       </c>
-      <c r="Q4" s="21" t="n">
+      <c r="Q4" s="22" t="n">
         <v>350</v>
       </c>
-      <c r="R4" s="21" t="n">
+      <c r="R4" s="22" t="n">
         <v>25</v>
       </c>
     </row>
@@ -5535,115 +5057,291 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:XFD16"/>
-  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:XFD21"/>
+  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="2" width="29.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="40.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="29.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="40.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="29.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="40.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="2" width="29.34"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="12" min="12" style="12" width="11"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16383" min="13" style="2" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="26.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="63.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="2" width="26.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="54.46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="30.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="68.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="26.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="2" width="30.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="2" width="26.66"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16381" min="12" style="2" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16382" style="3" width="10.49"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="19" t="s">
-        <v>235</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
+      <c r="A1" s="20" t="s">
+        <v>217</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
     </row>
     <row r="2" s="7" customFormat="true" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="20" t="s">
-        <v>260</v>
-      </c>
-      <c r="D2" s="20" t="s">
-        <v>261</v>
-      </c>
-      <c r="E2" s="20" t="s">
-        <v>262</v>
-      </c>
-      <c r="F2" s="20" t="s">
-        <v>263</v>
-      </c>
-      <c r="G2" s="20" t="s">
-        <v>264</v>
-      </c>
-      <c r="H2" s="20" t="s">
-        <v>265</v>
-      </c>
-      <c r="I2" s="20" t="s">
-        <v>266</v>
-      </c>
-      <c r="J2" s="20" t="s">
-        <v>267</v>
-      </c>
-      <c r="K2" s="20" t="s">
-        <v>268</v>
-      </c>
-      <c r="L2" s="12"/>
-      <c r="XFD2" s="0"/>
+      <c r="C2" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="D2" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="E2" s="21" t="s">
+        <v>242</v>
+      </c>
+      <c r="F2" s="21" t="s">
+        <v>243</v>
+      </c>
+      <c r="G2" s="21" t="s">
+        <v>244</v>
+      </c>
+      <c r="H2" s="21" t="s">
+        <v>245</v>
+      </c>
+      <c r="I2" s="21" t="s">
+        <v>246</v>
+      </c>
+      <c r="J2" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="K2" s="21" t="s">
+        <v>248</v>
+      </c>
+      <c r="XFB2" s="3"/>
+      <c r="XFC2" s="3"/>
+      <c r="XFD2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="21" t="s">
-        <v>145</v>
-      </c>
-      <c r="B3" s="21" t="s">
-        <v>269</v>
-      </c>
-      <c r="C3" s="21" t="b">
+      <c r="A3" s="22" t="s">
+        <v>136</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>249</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>250</v>
+      </c>
+      <c r="D3" s="22" t="s">
+        <v>251</v>
+      </c>
+      <c r="E3" s="22" t="s">
+        <v>252</v>
+      </c>
+      <c r="F3" s="22" t="s">
+        <v>253</v>
+      </c>
+      <c r="G3" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="D3" s="21" t="s">
-        <v>270</v>
-      </c>
-      <c r="E3" s="21" t="b">
+      <c r="H3" s="22" t="s">
+        <v>254</v>
+      </c>
+      <c r="I3" s="22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J3" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="K3" s="22" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="22" t="s">
+        <v>143</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>255</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>250</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>256</v>
+      </c>
+      <c r="E4" s="22" t="s">
+        <v>252</v>
+      </c>
+      <c r="F4" s="22" t="s">
+        <v>253</v>
+      </c>
+      <c r="G4" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="F3" s="21" t="s">
-        <v>271</v>
-      </c>
-      <c r="G3" s="21" t="b">
+      <c r="H4" s="22" t="s">
+        <v>254</v>
+      </c>
+      <c r="I4" s="22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J4" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="K4" s="22" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="22" t="s">
+        <v>158</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>257</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>250</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>251</v>
+      </c>
+      <c r="E5" s="22" t="s">
+        <v>252</v>
+      </c>
+      <c r="F5" s="22" t="s">
+        <v>258</v>
+      </c>
+      <c r="G5" s="22" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H3" s="21" t="s">
-        <v>272</v>
-      </c>
-      <c r="I3" s="21" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J3" s="21" t="n">
+      <c r="H5" s="22" t="s">
+        <v>259</v>
+      </c>
+      <c r="I5" s="22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J5" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="K3" s="21" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="5" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="6" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="7" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="8" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    </row>
+    <row r="6" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="22" t="s">
+        <v>161</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>260</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>250</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>256</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>252</v>
+      </c>
+      <c r="F6" s="22" t="s">
+        <v>258</v>
+      </c>
+      <c r="G6" s="22" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="H6" s="22" t="s">
+        <v>259</v>
+      </c>
+      <c r="I6" s="22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J6" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" s="22" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="22" t="s">
+        <v>182</v>
+      </c>
+      <c r="B7" s="22" t="s">
+        <v>261</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>250</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>262</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>252</v>
+      </c>
+      <c r="F7" s="22" t="s">
+        <v>253</v>
+      </c>
+      <c r="G7" s="22" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="H7" s="22" t="s">
+        <v>254</v>
+      </c>
+      <c r="I7" s="22" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J7" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" s="22" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>263</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>250</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>262</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>252</v>
+      </c>
+      <c r="F8" s="22" t="s">
+        <v>258</v>
+      </c>
+      <c r="G8" s="22" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="H8" s="22" t="s">
+        <v>259</v>
+      </c>
+      <c r="I8" s="22" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J8" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="K8" s="22" t="n">
+        <v>6</v>
+      </c>
+    </row>
     <row r="9" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -5652,6 +5350,11 @@
     <row r="14" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="15" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="16" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="17" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="18" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="19" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="20" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="21" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:K1"/>
